--- a/model performance comparison/Amount_Cell_Media/Truisi 2015/Results/Fischer model_PHH.xlsx
+++ b/model performance comparison/Amount_Cell_Media/Truisi 2015/Results/Fischer model_PHH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\New dataset from SOT poster\Truisi 2015\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\New dataset from SOT poster\Truisi 2015\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEBC2FE-EA25-4FE0-BFDF-77565F76C67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BF2076-9DE8-4FD7-B6D0-715DBE012EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1984,143 +1984,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -2208,6 +2071,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2234,6 +2103,137 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -14056,8 +14056,8 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14090,19 +14090,19 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="156" t="s">
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="158"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="120"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14126,17 +14126,17 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160"/>
-      <c r="Q3" s="161"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="123"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14160,17 +14160,17 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="162"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
-      <c r="O4" s="163"/>
-      <c r="P4" s="163"/>
-      <c r="Q4" s="164"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="173"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="125"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="126"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14194,19 +14194,19 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="165" t="s">
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="166"/>
-      <c r="K5" s="166"/>
-      <c r="L5" s="166"/>
-      <c r="M5" s="166"/>
-      <c r="N5" s="166"/>
-      <c r="O5" s="166"/>
-      <c r="P5" s="166"/>
-      <c r="Q5" s="167"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="129"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14230,8 +14230,8 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="143"/>
-      <c r="H6" s="143"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="173"/>
       <c r="I6" s="50" t="s">
         <v>49</v>
       </c>
@@ -14241,14 +14241,14 @@
       <c r="K6" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="135" t="s">
+      <c r="L6" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="136"/>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="137"/>
+      <c r="M6" s="171"/>
+      <c r="N6" s="171"/>
+      <c r="O6" s="171"/>
+      <c r="P6" s="171"/>
+      <c r="Q6" s="172"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14272,8 +14272,8 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="143"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="173"/>
       <c r="I7" s="51" t="s">
         <v>20</v>
       </c>
@@ -14285,14 +14285,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="118" t="s">
+      <c r="L7" s="164" t="s">
         <v>68</v>
       </c>
-      <c r="M7" s="119"/>
-      <c r="N7" s="119"/>
-      <c r="O7" s="119"/>
-      <c r="P7" s="119"/>
-      <c r="Q7" s="120"/>
+      <c r="M7" s="165"/>
+      <c r="N7" s="165"/>
+      <c r="O7" s="165"/>
+      <c r="P7" s="165"/>
+      <c r="Q7" s="166"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14311,15 +14311,15 @@
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="181" t="s">
+      <c r="B8" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="182"/>
-      <c r="D8" s="182"/>
-      <c r="E8" s="182"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
+      <c r="C8" s="146"/>
+      <c r="D8" s="146"/>
+      <c r="E8" s="146"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14331,14 +14331,14 @@
         <f>J8/J7</f>
         <v>0.99957135230126803</v>
       </c>
-      <c r="L8" s="118" t="s">
+      <c r="L8" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="119"/>
-      <c r="N8" s="119"/>
-      <c r="O8" s="119"/>
-      <c r="P8" s="119"/>
-      <c r="Q8" s="120"/>
+      <c r="M8" s="165"/>
+      <c r="N8" s="165"/>
+      <c r="O8" s="165"/>
+      <c r="P8" s="165"/>
+      <c r="Q8" s="166"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14357,13 +14357,13 @@
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="185"/>
-      <c r="F9" s="186"/>
-      <c r="G9" s="143"/>
-      <c r="H9" s="143"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="149"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="173"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14375,14 +14375,14 @@
         <f>J9/J7</f>
         <v>3.2055393122561453E-4</v>
       </c>
-      <c r="L9" s="118" t="s">
+      <c r="L9" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M9" s="119"/>
-      <c r="N9" s="119"/>
-      <c r="O9" s="119"/>
-      <c r="P9" s="119"/>
-      <c r="Q9" s="120"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="165"/>
+      <c r="O9" s="165"/>
+      <c r="P9" s="165"/>
+      <c r="Q9" s="166"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14401,13 +14401,13 @@
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="187"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="188"/>
-      <c r="F10" s="189"/>
-      <c r="G10" s="143"/>
-      <c r="H10" s="143"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="152"/>
+      <c r="E10" s="152"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="173"/>
+      <c r="H10" s="173"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14419,14 +14419,14 @@
         <f>J10/J7</f>
         <v>1.0809376750631187E-4</v>
       </c>
-      <c r="L10" s="118" t="s">
+      <c r="L10" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="119"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="119"/>
-      <c r="P10" s="119"/>
-      <c r="Q10" s="120"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="165"/>
+      <c r="O10" s="165"/>
+      <c r="P10" s="165"/>
+      <c r="Q10" s="166"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14445,24 +14445,24 @@
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="146" t="s">
+      <c r="B11" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="143"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="134"/>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="173"/>
+      <c r="H11" s="173"/>
+      <c r="I11" s="189"/>
+      <c r="J11" s="189"/>
+      <c r="K11" s="189"/>
+      <c r="L11" s="189"/>
+      <c r="M11" s="189"/>
+      <c r="N11" s="189"/>
+      <c r="O11" s="189"/>
+      <c r="P11" s="189"/>
+      <c r="Q11" s="189"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14481,13 +14481,13 @@
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="149"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="143"/>
+      <c r="B12" s="157"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
       <c r="I12" s="50" t="s">
         <v>51</v>
       </c>
@@ -14497,14 +14497,14 @@
       <c r="K12" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="135" t="s">
+      <c r="L12" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="M12" s="136"/>
-      <c r="N12" s="136"/>
-      <c r="O12" s="136"/>
-      <c r="P12" s="136"/>
-      <c r="Q12" s="137"/>
+      <c r="M12" s="171"/>
+      <c r="N12" s="171"/>
+      <c r="O12" s="171"/>
+      <c r="P12" s="171"/>
+      <c r="Q12" s="172"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14523,17 +14523,17 @@
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="138" t="s">
+      <c r="B13" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="139"/>
-      <c r="D13" s="171" t="s">
+      <c r="C13" s="144"/>
+      <c r="D13" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="171"/>
-      <c r="F13" s="171"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="143"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14545,14 +14545,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="118" t="s">
+      <c r="L13" s="164" t="s">
         <v>71</v>
       </c>
-      <c r="M13" s="119"/>
-      <c r="N13" s="119"/>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="120"/>
+      <c r="M13" s="165"/>
+      <c r="N13" s="165"/>
+      <c r="O13" s="165"/>
+      <c r="P13" s="165"/>
+      <c r="Q13" s="166"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14577,13 +14577,13 @@
       <c r="C14" s="44">
         <v>2000</v>
       </c>
-      <c r="D14" s="172" t="s">
+      <c r="D14" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="172"/>
-      <c r="F14" s="172"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="143"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="173"/>
       <c r="I14" s="52" t="s">
         <v>43</v>
       </c>
@@ -14595,14 +14595,14 @@
         <f>J14/J13</f>
         <v>1</v>
       </c>
-      <c r="L14" s="140" t="s">
+      <c r="L14" s="167" t="s">
         <v>70</v>
       </c>
-      <c r="M14" s="141"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="141"/>
-      <c r="P14" s="141"/>
-      <c r="Q14" s="142"/>
+      <c r="M14" s="168"/>
+      <c r="N14" s="168"/>
+      <c r="O14" s="168"/>
+      <c r="P14" s="168"/>
+      <c r="Q14" s="169"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14627,13 +14627,13 @@
       <c r="C15" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="173" t="s">
+      <c r="D15" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="173"/>
-      <c r="F15" s="173"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="143"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="173"/>
       <c r="I15" s="51" t="s">
         <v>44</v>
       </c>
@@ -14645,14 +14645,14 @@
         <f>J15/J13</f>
         <v>0</v>
       </c>
-      <c r="L15" s="118" t="s">
+      <c r="L15" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="119"/>
-      <c r="N15" s="119"/>
-      <c r="O15" s="119"/>
-      <c r="P15" s="119"/>
-      <c r="Q15" s="120"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="165"/>
+      <c r="O15" s="165"/>
+      <c r="P15" s="165"/>
+      <c r="Q15" s="166"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14677,13 +14677,13 @@
       <c r="C16" s="45">
         <v>1</v>
       </c>
-      <c r="D16" s="174" t="s">
+      <c r="D16" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="175"/>
-      <c r="F16" s="176"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="143"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="173"/>
       <c r="I16" s="52" t="s">
         <v>45</v>
       </c>
@@ -14695,14 +14695,14 @@
         <f>J16/J13</f>
         <v>0</v>
       </c>
-      <c r="L16" s="118" t="s">
+      <c r="L16" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M16" s="119"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="120"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="165"/>
+      <c r="O16" s="165"/>
+      <c r="P16" s="165"/>
+      <c r="Q16" s="166"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14727,22 +14727,22 @@
       <c r="C17" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="177" t="s">
+      <c r="D17" s="139" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="140"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="141"/>
-      <c r="O17" s="141"/>
-      <c r="P17" s="141"/>
-      <c r="Q17" s="142"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="167"/>
+      <c r="J17" s="168"/>
+      <c r="K17" s="168"/>
+      <c r="L17" s="168"/>
+      <c r="M17" s="168"/>
+      <c r="N17" s="168"/>
+      <c r="O17" s="168"/>
+      <c r="P17" s="168"/>
+      <c r="Q17" s="169"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14767,13 +14767,13 @@
       <c r="C18" s="45">
         <v>0</v>
       </c>
-      <c r="D18" s="174" t="s">
+      <c r="D18" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="175"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="143"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="173"/>
       <c r="I18" s="50" t="s">
         <v>29</v>
       </c>
@@ -14783,14 +14783,14 @@
       <c r="K18" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="L18" s="135" t="s">
+      <c r="L18" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="M18" s="136"/>
-      <c r="N18" s="136"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="136"/>
-      <c r="Q18" s="137"/>
+      <c r="M18" s="171"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="171"/>
+      <c r="P18" s="171"/>
+      <c r="Q18" s="172"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14809,13 +14809,13 @@
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="173"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="173"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="143"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="173"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14827,14 +14827,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="118" t="s">
+      <c r="L19" s="164" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="119"/>
-      <c r="N19" s="119"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="120"/>
+      <c r="M19" s="165"/>
+      <c r="N19" s="165"/>
+      <c r="O19" s="165"/>
+      <c r="P19" s="165"/>
+      <c r="Q19" s="166"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14853,17 +14853,17 @@
     </row>
     <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="138" t="s">
+      <c r="B20" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="139"/>
-      <c r="D20" s="171" t="s">
+      <c r="C20" s="144"/>
+      <c r="D20" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="171"/>
-      <c r="F20" s="171"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="143"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="173"/>
       <c r="I20" s="52" t="s">
         <v>43</v>
       </c>
@@ -14875,14 +14875,14 @@
         <f>J20/J19</f>
         <v>0.87305569493226298</v>
       </c>
-      <c r="L20" s="118" t="s">
+      <c r="L20" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M20" s="119"/>
-      <c r="N20" s="119"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="119"/>
-      <c r="Q20" s="120"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="165"/>
+      <c r="O20" s="165"/>
+      <c r="P20" s="165"/>
+      <c r="Q20" s="166"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14907,13 +14907,13 @@
       <c r="C21" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="177" t="s">
+      <c r="D21" s="139" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="143"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="173"/>
+      <c r="H21" s="173"/>
       <c r="I21" s="51" t="s">
         <v>44</v>
       </c>
@@ -14925,14 +14925,14 @@
         <f>J21/J19</f>
         <v>9.4932262920220778E-2</v>
       </c>
-      <c r="L21" s="118" t="s">
+      <c r="L21" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M21" s="119"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="120"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="165"/>
+      <c r="O21" s="165"/>
+      <c r="P21" s="165"/>
+      <c r="Q21" s="166"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -14957,13 +14957,13 @@
       <c r="C22" s="46">
         <v>2000000</v>
       </c>
-      <c r="D22" s="180" t="s">
+      <c r="D22" s="142" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="180"/>
-      <c r="F22" s="180"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="143"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
       <c r="I22" s="53" t="s">
         <v>45</v>
       </c>
@@ -14975,14 +14975,14 @@
         <f>J22/J19</f>
         <v>3.2012042147516309E-2</v>
       </c>
-      <c r="L22" s="118" t="s">
+      <c r="L22" s="164" t="s">
         <v>69</v>
       </c>
-      <c r="M22" s="119"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="120"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="165"/>
+      <c r="O22" s="165"/>
+      <c r="P22" s="165"/>
+      <c r="Q22" s="166"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -15001,22 +15001,22 @@
     </row>
     <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="168"/>
-      <c r="C23" s="169"/>
-      <c r="D23" s="169"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="170"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="143"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="130"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="130"/>
-      <c r="M23" s="130"/>
-      <c r="N23" s="130"/>
-      <c r="O23" s="130"/>
-      <c r="P23" s="130"/>
-      <c r="Q23" s="131"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="185"/>
+      <c r="K23" s="185"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="185"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="185"/>
+      <c r="P23" s="185"/>
+      <c r="Q23" s="186"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -15035,26 +15035,26 @@
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="146" t="s">
+      <c r="B24" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="123" t="s">
+      <c r="C24" s="155"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="156"/>
+      <c r="G24" s="173"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="125"/>
+      <c r="J24" s="179"/>
+      <c r="K24" s="179"/>
+      <c r="L24" s="179"/>
+      <c r="M24" s="179"/>
+      <c r="N24" s="179"/>
+      <c r="O24" s="179"/>
+      <c r="P24" s="179"/>
+      <c r="Q24" s="180"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15073,22 +15073,22 @@
     </row>
     <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="149"/>
-      <c r="C25" s="150"/>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="127"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127"/>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="128"/>
+      <c r="B25" s="157"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="173"/>
+      <c r="H25" s="173"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="182"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="182"/>
+      <c r="Q25" s="183"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15107,48 +15107,48 @@
     </row>
     <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="176" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="152" t="s">
+      <c r="D26" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="152" t="s">
+      <c r="E26" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="154" t="s">
+      <c r="F26" s="162" t="s">
         <v>66</v>
       </c>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="132" t="s">
+      <c r="G26" s="173"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="187" t="s">
         <v>53</v>
       </c>
-      <c r="J26" s="132" t="s">
+      <c r="J26" s="187" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="121" t="s">
+      <c r="K26" s="174" t="s">
         <v>74</v>
       </c>
-      <c r="L26" s="121" t="s">
+      <c r="L26" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="M26" s="121" t="s">
+      <c r="M26" s="174" t="s">
         <v>59</v>
       </c>
-      <c r="N26" s="121" t="s">
+      <c r="N26" s="174" t="s">
         <v>62</v>
       </c>
-      <c r="O26" s="121" t="s">
+      <c r="O26" s="174" t="s">
         <v>73</v>
       </c>
-      <c r="P26" s="121" t="s">
+      <c r="P26" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="Q26" s="121" t="s">
+      <c r="Q26" s="174" t="s">
         <v>65</v>
       </c>
       <c r="R26" s="9"/>
@@ -15169,22 +15169,22 @@
     </row>
     <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="145"/>
-      <c r="C27" s="145"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="155"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="143"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="122"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="122"/>
+      <c r="B27" s="177"/>
+      <c r="C27" s="177"/>
+      <c r="D27" s="161"/>
+      <c r="E27" s="161"/>
+      <c r="F27" s="163"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="188"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="175"/>
+      <c r="L27" s="175"/>
+      <c r="M27" s="175"/>
+      <c r="N27" s="175"/>
+      <c r="O27" s="175"/>
+      <c r="P27" s="175"/>
+      <c r="Q27" s="175"/>
       <c r="R27" s="7" t="s">
         <v>84</v>
       </c>
@@ -15222,8 +15222,8 @@
       <c r="F28" s="103">
         <v>2.4999999999999999E-7</v>
       </c>
-      <c r="G28" s="143"/>
-      <c r="H28" s="143"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="173"/>
       <c r="I28" s="99">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
         <v>0</v>
@@ -15268,8 +15268,11 @@
         <f>R28*L28</f>
         <v>4.9999344071532731E-4</v>
       </c>
-      <c r="T28" s="9"/>
-      <c r="U28" s="7"/>
+      <c r="T28" s="9">
+        <f>R28*M28</f>
+        <v>6.5592846726914013E-9</v>
+      </c>
+      <c r="U28" s="9"/>
       <c r="V28" s="7"/>
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
@@ -15299,8 +15302,8 @@
       <c r="F29" s="103">
         <v>2.5000000000000002E-6</v>
       </c>
-      <c r="G29" s="143"/>
-      <c r="H29" s="143"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="173"/>
       <c r="I29" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -15342,11 +15345,14 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S29" s="11">
-        <f t="shared" ref="S29:S31" si="11">R29*L29</f>
+        <f t="shared" ref="S29" si="11">R29*L29</f>
         <v>4.9999344071532731E-3</v>
       </c>
-      <c r="T29" s="9"/>
-      <c r="U29" s="7"/>
+      <c r="T29" s="9">
+        <f>R29*M29</f>
+        <v>6.5592846726914008E-8</v>
+      </c>
+      <c r="U29" s="9"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
@@ -15368,61 +15374,64 @@
         <v>87</v>
       </c>
       <c r="D30" s="95">
-        <v>2.9091840000000002</v>
+        <v>1.6452318246143236</v>
       </c>
       <c r="E30" s="95">
-        <v>3.4102429999999995</v>
+        <v>1.8629354124795308</v>
       </c>
       <c r="F30" s="103">
         <v>9.9999999999999991E-5</v>
       </c>
-      <c r="G30" s="143"/>
-      <c r="H30" s="143"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="173"/>
       <c r="I30" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J30" s="99">
         <f t="shared" si="2"/>
-        <v>2.2047213875633358</v>
+        <v>0.8693500964236418</v>
       </c>
       <c r="K30" s="100">
         <f t="shared" si="3"/>
-        <v>0.64815232221089381</v>
+        <v>0.97553478282274741</v>
       </c>
       <c r="L30" s="100">
         <f t="shared" si="4"/>
-        <v>0.35184767778910619</v>
+        <v>2.4465217177252644E-2</v>
       </c>
       <c r="M30" s="100">
         <f t="shared" si="5"/>
-        <v>0.64815232221089381</v>
+        <v>0.9755347828227473</v>
       </c>
       <c r="N30" s="100">
         <f t="shared" si="6"/>
-        <v>0.1807963595648138</v>
+        <v>7.7169870492751671E-3</v>
       </c>
       <c r="O30" s="41">
         <f t="shared" si="7"/>
-        <v>6.5034832709377636E-5</v>
+        <v>9.7883999222042915E-5</v>
       </c>
       <c r="P30" s="41">
         <f t="shared" si="8"/>
-        <v>1.0419992707010521E-2</v>
+        <v>7.2453905668577951E-4</v>
       </c>
       <c r="Q30" s="41">
         <f t="shared" si="9"/>
-        <v>0.16725881957464073</v>
+        <v>7.139160034203223E-3</v>
       </c>
       <c r="R30" s="9">
         <f t="shared" si="10"/>
         <v>0.19999999999999998</v>
       </c>
       <c r="S30" s="11">
-        <f t="shared" si="11"/>
-        <v>7.0369535557821231E-2</v>
-      </c>
-      <c r="T30" s="7"/>
+        <f>R30*L30</f>
+        <v>4.8930434354505286E-3</v>
+      </c>
+      <c r="T30" s="9">
+        <f>R30*M30</f>
+        <v>0.19510695656454943</v>
+      </c>
       <c r="U30" s="7"/>
       <c r="V30" s="7"/>
       <c r="W30" s="7"/>
@@ -15445,61 +15454,64 @@
         <v>87</v>
       </c>
       <c r="D31" s="95">
-        <v>2.9091840000000002</v>
+        <v>1.6452318246143236</v>
       </c>
       <c r="E31" s="95">
-        <v>3.4102429999999995</v>
+        <v>1.8629354124795308</v>
       </c>
       <c r="F31" s="98">
         <v>1E-3</v>
       </c>
-      <c r="G31" s="143"/>
-      <c r="H31" s="143"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="173"/>
       <c r="I31" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J31" s="99">
         <f t="shared" si="2"/>
-        <v>2.2047213875633358</v>
+        <v>0.8693500964236418</v>
       </c>
       <c r="K31" s="100">
         <f t="shared" si="3"/>
-        <v>0.64815232221089381</v>
+        <v>0.97553478282274741</v>
       </c>
       <c r="L31" s="100">
         <f t="shared" si="4"/>
-        <v>0.35184767778910619</v>
+        <v>2.4465217177252644E-2</v>
       </c>
       <c r="M31" s="100">
         <f t="shared" si="5"/>
-        <v>0.64815232221089381</v>
+        <v>0.9755347828227473</v>
       </c>
       <c r="N31" s="100">
         <f t="shared" si="6"/>
-        <v>0.1807963595648138</v>
+        <v>7.7169870492751671E-3</v>
       </c>
       <c r="O31" s="41">
         <f t="shared" si="7"/>
-        <v>6.5034832709377657E-4</v>
+        <v>9.7883999222042909E-4</v>
       </c>
       <c r="P31" s="41">
         <f t="shared" si="8"/>
-        <v>0.10419992707010524</v>
+        <v>7.2453905668577951E-3</v>
       </c>
       <c r="Q31" s="41">
         <f t="shared" si="9"/>
-        <v>1.6725881957464073</v>
+        <v>7.1391600342032249E-2</v>
       </c>
       <c r="R31" s="9">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="S31" s="11">
-        <f t="shared" si="11"/>
-        <v>0.70369535557821239</v>
-      </c>
-      <c r="T31" s="7"/>
+        <f t="shared" ref="S31" si="12">R31*L31</f>
+        <v>4.8930434354505288E-2</v>
+      </c>
+      <c r="T31" s="9">
+        <f>R31*M31</f>
+        <v>1.9510695656454946</v>
+      </c>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
@@ -15520,8 +15532,8 @@
       <c r="D32" s="48"/>
       <c r="E32" s="48"/>
       <c r="F32" s="98"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="143"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="173"/>
       <c r="I32" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15581,8 +15593,8 @@
       <c r="D33" s="102"/>
       <c r="E33" s="102"/>
       <c r="F33" s="98"/>
-      <c r="G33" s="143"/>
-      <c r="H33" s="143"/>
+      <c r="G33" s="173"/>
+      <c r="H33" s="173"/>
       <c r="I33" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15642,8 +15654,8 @@
       <c r="D34" s="95"/>
       <c r="E34" s="95"/>
       <c r="F34" s="98"/>
-      <c r="G34" s="143"/>
-      <c r="H34" s="143"/>
+      <c r="G34" s="173"/>
+      <c r="H34" s="173"/>
       <c r="I34" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15703,8 +15715,8 @@
       <c r="D35" s="95"/>
       <c r="E35" s="95"/>
       <c r="F35" s="96"/>
-      <c r="G35" s="143"/>
-      <c r="H35" s="143"/>
+      <c r="G35" s="173"/>
+      <c r="H35" s="173"/>
       <c r="I35" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15764,8 +15776,8 @@
       <c r="D36" s="48"/>
       <c r="E36" s="48"/>
       <c r="F36" s="96"/>
-      <c r="G36" s="143"/>
-      <c r="H36" s="143"/>
+      <c r="G36" s="173"/>
+      <c r="H36" s="173"/>
       <c r="I36" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15825,8 +15837,8 @@
       <c r="D37" s="102"/>
       <c r="E37" s="102"/>
       <c r="F37" s="96"/>
-      <c r="G37" s="143"/>
-      <c r="H37" s="143"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
       <c r="I37" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15886,8 +15898,8 @@
       <c r="D38" s="95"/>
       <c r="E38" s="95"/>
       <c r="F38" s="96"/>
-      <c r="G38" s="143"/>
-      <c r="H38" s="143"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="173"/>
       <c r="I38" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -15947,8 +15959,8 @@
       <c r="D39" s="95"/>
       <c r="E39" s="95"/>
       <c r="F39" s="96"/>
-      <c r="G39" s="143"/>
-      <c r="H39" s="143"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="173"/>
       <c r="I39" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16008,8 +16020,8 @@
       <c r="D40" s="48"/>
       <c r="E40" s="48"/>
       <c r="F40" s="96"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="143"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
       <c r="I40" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16069,8 +16081,8 @@
       <c r="D41" s="102"/>
       <c r="E41" s="102"/>
       <c r="F41" s="96"/>
-      <c r="G41" s="143"/>
-      <c r="H41" s="143"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="173"/>
       <c r="I41" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16130,8 +16142,8 @@
       <c r="D42" s="95"/>
       <c r="E42" s="95"/>
       <c r="F42" s="96"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="143"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="173"/>
       <c r="I42" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16191,8 +16203,8 @@
       <c r="D43" s="95"/>
       <c r="E43" s="95"/>
       <c r="F43" s="96"/>
-      <c r="G43" s="143"/>
-      <c r="H43" s="143"/>
+      <c r="G43" s="173"/>
+      <c r="H43" s="173"/>
       <c r="I43" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16252,8 +16264,8 @@
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
       <c r="F44" s="96"/>
-      <c r="G44" s="143"/>
-      <c r="H44" s="143"/>
+      <c r="G44" s="173"/>
+      <c r="H44" s="173"/>
       <c r="I44" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16313,8 +16325,8 @@
       <c r="D45" s="95"/>
       <c r="E45" s="95"/>
       <c r="F45" s="96"/>
-      <c r="G45" s="143"/>
-      <c r="H45" s="143"/>
+      <c r="G45" s="173"/>
+      <c r="H45" s="173"/>
       <c r="I45" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16374,8 +16386,8 @@
       <c r="D46" s="97"/>
       <c r="E46" s="97"/>
       <c r="F46" s="96"/>
-      <c r="G46" s="143"/>
-      <c r="H46" s="143"/>
+      <c r="G46" s="173"/>
+      <c r="H46" s="173"/>
       <c r="I46" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16435,8 +16447,8 @@
       <c r="D47" s="95"/>
       <c r="E47" s="95"/>
       <c r="F47" s="96"/>
-      <c r="G47" s="143"/>
-      <c r="H47" s="143"/>
+      <c r="G47" s="173"/>
+      <c r="H47" s="173"/>
       <c r="I47" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16496,42 +16508,42 @@
       <c r="D48" s="95"/>
       <c r="E48" s="95"/>
       <c r="F48" s="96"/>
-      <c r="G48" s="143"/>
-      <c r="H48" s="143"/>
+      <c r="G48" s="173"/>
+      <c r="H48" s="173"/>
       <c r="I48" s="99" t="str">
-        <f t="shared" ref="I48:I50" si="12">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
+        <f t="shared" ref="I48:I50" si="13">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
         <v/>
       </c>
       <c r="J48" s="99" t="str">
-        <f t="shared" ref="J48:J50" si="13">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
+        <f t="shared" ref="J48:J50" si="14">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
         <v/>
       </c>
       <c r="K48" s="100" t="str">
-        <f t="shared" ref="K48:K50" si="14">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
+        <f t="shared" ref="K48:K50" si="15">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L48" s="100" t="str">
-        <f t="shared" ref="L48:L50" si="15">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
+        <f t="shared" ref="L48:L50" si="16">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M48" s="100" t="str">
-        <f t="shared" ref="M48:M92" si="16">IF(D48=0,"",1-L48)</f>
+        <f t="shared" ref="M48:M92" si="17">IF(D48=0,"",1-L48)</f>
         <v/>
       </c>
       <c r="N48" s="100" t="str">
-        <f t="shared" ref="N48:N50" si="17">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N48:N50" si="18">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O48" s="41" t="str">
-        <f t="shared" ref="O48:O92" si="18">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
+        <f t="shared" ref="O48:O92" si="19">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
         <v/>
       </c>
       <c r="P48" s="41" t="str">
-        <f t="shared" ref="P48:P50" si="19">IF(D48=0,"",O48*10^J48)</f>
+        <f t="shared" ref="P48:P50" si="20">IF(D48=0,"",O48*10^J48)</f>
         <v/>
       </c>
       <c r="Q48" s="41" t="str">
-        <f t="shared" ref="Q48:Q50" si="20">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
+        <f t="shared" ref="Q48:Q50" si="21">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R48" s="7"/>
@@ -16557,42 +16569,42 @@
       <c r="D49" s="95"/>
       <c r="E49" s="95"/>
       <c r="F49" s="96"/>
-      <c r="G49" s="143"/>
-      <c r="H49" s="143"/>
+      <c r="G49" s="173"/>
+      <c r="H49" s="173"/>
       <c r="I49" s="99" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J49" s="99" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K49" s="100" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="L49" s="100" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="M49" s="100" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N49" s="100" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="O49" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P49" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q49" s="41" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R49" s="7"/>
@@ -16618,42 +16630,42 @@
       <c r="D50" s="95"/>
       <c r="E50" s="95"/>
       <c r="F50" s="96"/>
-      <c r="G50" s="143"/>
-      <c r="H50" s="143"/>
+      <c r="G50" s="173"/>
+      <c r="H50" s="173"/>
       <c r="I50" s="99" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J50" s="99" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K50" s="100" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="L50" s="100" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="M50" s="100" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N50" s="100" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="O50" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P50" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q50" s="41" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R50" s="7"/>
@@ -16679,42 +16691,42 @@
       <c r="D51" s="95"/>
       <c r="E51" s="95"/>
       <c r="F51" s="96"/>
-      <c r="G51" s="143"/>
-      <c r="H51" s="143"/>
+      <c r="G51" s="173"/>
+      <c r="H51" s="173"/>
       <c r="I51" s="99" t="str">
-        <f t="shared" ref="I51:I70" si="21">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
+        <f t="shared" ref="I51:I70" si="22">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
         <v/>
       </c>
       <c r="J51" s="99" t="str">
-        <f t="shared" ref="J51:J70" si="22">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
+        <f t="shared" ref="J51:J70" si="23">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
         <v/>
       </c>
       <c r="K51" s="100" t="str">
-        <f t="shared" ref="K51:K70" si="23">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
+        <f t="shared" ref="K51:K70" si="24">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L51" s="100" t="str">
-        <f t="shared" ref="L51:L70" si="24">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
+        <f t="shared" ref="L51:L70" si="25">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M51" s="100" t="str">
-        <f t="shared" ref="M51:M70" si="25">IF(D51=0,"",1-L51)</f>
+        <f t="shared" ref="M51:M70" si="26">IF(D51=0,"",1-L51)</f>
         <v/>
       </c>
       <c r="N51" s="100" t="str">
-        <f t="shared" ref="N51:N70" si="26">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N51:N70" si="27">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O51" s="41" t="str">
-        <f t="shared" ref="O51:O70" si="27">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
+        <f t="shared" ref="O51:O70" si="28">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
         <v/>
       </c>
       <c r="P51" s="41" t="str">
-        <f t="shared" ref="P51:P70" si="28">IF(D51=0,"",O51*10^J51)</f>
+        <f t="shared" ref="P51:P70" si="29">IF(D51=0,"",O51*10^J51)</f>
         <v/>
       </c>
       <c r="Q51" s="41" t="str">
-        <f t="shared" ref="Q51:Q70" si="29">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
+        <f t="shared" ref="Q51:Q70" si="30">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R51" s="7"/>
@@ -16740,42 +16752,42 @@
       <c r="D52" s="48"/>
       <c r="E52" s="48"/>
       <c r="F52" s="96"/>
-      <c r="G52" s="143"/>
-      <c r="H52" s="143"/>
+      <c r="G52" s="173"/>
+      <c r="H52" s="173"/>
       <c r="I52" s="99" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J52" s="99" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K52" s="100" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L52" s="100" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M52" s="100" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N52" s="100" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O52" s="41" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P52" s="41" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q52" s="41" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R52" s="7"/>
@@ -16801,42 +16813,42 @@
       <c r="D53" s="48"/>
       <c r="E53" s="48"/>
       <c r="F53" s="96"/>
-      <c r="G53" s="143"/>
-      <c r="H53" s="143"/>
+      <c r="G53" s="173"/>
+      <c r="H53" s="173"/>
       <c r="I53" s="99" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J53" s="99" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K53" s="100" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L53" s="100" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M53" s="100" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N53" s="100" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O53" s="41" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P53" s="41" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q53" s="41" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R53" s="7"/>
@@ -16862,42 +16874,42 @@
       <c r="D54" s="48"/>
       <c r="E54" s="48"/>
       <c r="F54" s="96"/>
-      <c r="G54" s="143"/>
-      <c r="H54" s="143"/>
+      <c r="G54" s="173"/>
+      <c r="H54" s="173"/>
       <c r="I54" s="99" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J54" s="99" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K54" s="100" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L54" s="100" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M54" s="100" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N54" s="100" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O54" s="41" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P54" s="41" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q54" s="41" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R54" s="7"/>
@@ -16923,42 +16935,42 @@
       <c r="D55" s="48"/>
       <c r="E55" s="48"/>
       <c r="F55" s="58"/>
-      <c r="G55" s="143"/>
-      <c r="H55" s="143"/>
+      <c r="G55" s="173"/>
+      <c r="H55" s="173"/>
       <c r="I55" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J55" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K55" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L55" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M55" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N55" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O55" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P55" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q55" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R55" s="7"/>
@@ -16984,42 +16996,42 @@
       <c r="D56" s="48"/>
       <c r="E56" s="48"/>
       <c r="F56" s="58"/>
-      <c r="G56" s="143"/>
-      <c r="H56" s="143"/>
+      <c r="G56" s="173"/>
+      <c r="H56" s="173"/>
       <c r="I56" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J56" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K56" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L56" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M56" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N56" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O56" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P56" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q56" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R56" s="7"/>
@@ -17045,42 +17057,42 @@
       <c r="D57" s="95"/>
       <c r="E57" s="95"/>
       <c r="F57" s="96"/>
-      <c r="G57" s="143"/>
-      <c r="H57" s="143"/>
+      <c r="G57" s="173"/>
+      <c r="H57" s="173"/>
       <c r="I57" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J57" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K57" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L57" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M57" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N57" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O57" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P57" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q57" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R57" s="7"/>
@@ -17106,42 +17118,42 @@
       <c r="D58" s="48"/>
       <c r="E58" s="48"/>
       <c r="F58" s="58"/>
-      <c r="G58" s="143"/>
-      <c r="H58" s="143"/>
+      <c r="G58" s="173"/>
+      <c r="H58" s="173"/>
       <c r="I58" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J58" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K58" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L58" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M58" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N58" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O58" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P58" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q58" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R58" s="7"/>
@@ -17167,42 +17179,42 @@
       <c r="D59" s="48"/>
       <c r="E59" s="48"/>
       <c r="F59" s="58"/>
-      <c r="G59" s="143"/>
-      <c r="H59" s="143"/>
+      <c r="G59" s="173"/>
+      <c r="H59" s="173"/>
       <c r="I59" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J59" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K59" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L59" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M59" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N59" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O59" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P59" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q59" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R59" s="7"/>
@@ -17228,42 +17240,42 @@
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
       <c r="F60" s="58"/>
-      <c r="G60" s="143"/>
-      <c r="H60" s="143"/>
+      <c r="G60" s="173"/>
+      <c r="H60" s="173"/>
       <c r="I60" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J60" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K60" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L60" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M60" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N60" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O60" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P60" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q60" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R60" s="7"/>
@@ -17289,42 +17301,42 @@
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="58"/>
-      <c r="G61" s="143"/>
-      <c r="H61" s="143"/>
+      <c r="G61" s="173"/>
+      <c r="H61" s="173"/>
       <c r="I61" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J61" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K61" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L61" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M61" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N61" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O61" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P61" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q61" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R61" s="7"/>
@@ -17350,42 +17362,42 @@
       <c r="D62" s="48"/>
       <c r="E62" s="48"/>
       <c r="F62" s="58"/>
-      <c r="G62" s="143"/>
-      <c r="H62" s="143"/>
+      <c r="G62" s="173"/>
+      <c r="H62" s="173"/>
       <c r="I62" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J62" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K62" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L62" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M62" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N62" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O62" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P62" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q62" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R62" s="7"/>
@@ -17411,42 +17423,42 @@
       <c r="D63" s="48"/>
       <c r="E63" s="48"/>
       <c r="F63" s="58"/>
-      <c r="G63" s="143"/>
-      <c r="H63" s="143"/>
+      <c r="G63" s="173"/>
+      <c r="H63" s="173"/>
       <c r="I63" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J63" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K63" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L63" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M63" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N63" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O63" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P63" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q63" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R63" s="7"/>
@@ -17472,42 +17484,42 @@
       <c r="D64" s="48"/>
       <c r="E64" s="48"/>
       <c r="F64" s="58"/>
-      <c r="G64" s="143"/>
-      <c r="H64" s="143"/>
+      <c r="G64" s="173"/>
+      <c r="H64" s="173"/>
       <c r="I64" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J64" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K64" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L64" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M64" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N64" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O64" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P64" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q64" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R64" s="7"/>
@@ -17533,42 +17545,42 @@
       <c r="D65" s="48"/>
       <c r="E65" s="48"/>
       <c r="F65" s="58"/>
-      <c r="G65" s="143"/>
-      <c r="H65" s="143"/>
+      <c r="G65" s="173"/>
+      <c r="H65" s="173"/>
       <c r="I65" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J65" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K65" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L65" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M65" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N65" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O65" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P65" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q65" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R65" s="7"/>
@@ -17594,42 +17606,42 @@
       <c r="D66" s="48"/>
       <c r="E66" s="48"/>
       <c r="F66" s="58"/>
-      <c r="G66" s="143"/>
-      <c r="H66" s="143"/>
+      <c r="G66" s="173"/>
+      <c r="H66" s="173"/>
       <c r="I66" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J66" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K66" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L66" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M66" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N66" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O66" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P66" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q66" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R66" s="7"/>
@@ -17655,42 +17667,42 @@
       <c r="D67" s="48"/>
       <c r="E67" s="48"/>
       <c r="F67" s="58"/>
-      <c r="G67" s="143"/>
-      <c r="H67" s="143"/>
+      <c r="G67" s="173"/>
+      <c r="H67" s="173"/>
       <c r="I67" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J67" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K67" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L67" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M67" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N67" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O67" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P67" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q67" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R67" s="7"/>
@@ -17716,42 +17728,42 @@
       <c r="D68" s="48"/>
       <c r="E68" s="48"/>
       <c r="F68" s="58"/>
-      <c r="G68" s="143"/>
-      <c r="H68" s="143"/>
+      <c r="G68" s="173"/>
+      <c r="H68" s="173"/>
       <c r="I68" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J68" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K68" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L68" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M68" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N68" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O68" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P68" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q68" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R68" s="7"/>
@@ -17777,42 +17789,42 @@
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="143"/>
-      <c r="H69" s="143"/>
+      <c r="G69" s="173"/>
+      <c r="H69" s="173"/>
       <c r="I69" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J69" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K69" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L69" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M69" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N69" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O69" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P69" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q69" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R69" s="7"/>
@@ -17838,42 +17850,42 @@
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70" s="58"/>
-      <c r="G70" s="143"/>
-      <c r="H70" s="143"/>
+      <c r="G70" s="173"/>
+      <c r="H70" s="173"/>
       <c r="I70" s="55" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J70" s="55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K70" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L70" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M70" s="56" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N70" s="56" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O70" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P70" s="57" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q70" s="57" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="R70" s="7"/>
@@ -17899,42 +17911,42 @@
       <c r="D71" s="48"/>
       <c r="E71" s="48"/>
       <c r="F71" s="58"/>
-      <c r="G71" s="143"/>
-      <c r="H71" s="143"/>
+      <c r="G71" s="173"/>
+      <c r="H71" s="173"/>
       <c r="I71" s="55" t="str">
-        <f t="shared" ref="I71:I122" si="30">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
+        <f t="shared" ref="I71:I122" si="31">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
         <v/>
       </c>
       <c r="J71" s="55" t="str">
-        <f t="shared" ref="J71:J122" si="31">IF(D71=0,"",LOG($K$21*10^D71+$K$22*10^E71+$K$20))</f>
+        <f t="shared" ref="J71:J122" si="32">IF(D71=0,"",LOG($K$21*10^D71+$K$22*10^E71+$K$20))</f>
         <v/>
       </c>
       <c r="K71" s="56" t="str">
-        <f t="shared" ref="K71:K122" si="32">IF(D71=0,"",1/(1+10^D71*$J$15/$J$14+10^E71*$J$16/$J$14+10^J71*$J$19/$J$14))</f>
+        <f t="shared" ref="K71:K122" si="33">IF(D71=0,"",1/(1+10^D71*$J$15/$J$14+10^E71*$J$16/$J$14+10^J71*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L71" s="56" t="str">
-        <f t="shared" ref="L71:L122" si="33">IF(D71=0,"",1/(1+10^I71/10^J71*$J$13/$J$19))</f>
+        <f t="shared" ref="L71:L122" si="34">IF(D71=0,"",1/(1+10^I71/10^J71*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M71" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N71" s="56" t="str">
-        <f t="shared" ref="N71:N122" si="34">IF(D71=0,"",1/(1/10^E71*$J$20/$J$22+10^D71/10^E71*$J$21/$J$22+10^I71/10^E71*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N71:N122" si="35">IF(D71=0,"",1/(1/10^E71*$J$20/$J$22+10^D71/10^E71*$J$21/$J$22+10^I71/10^E71*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O71" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P71" s="57" t="str">
-        <f t="shared" ref="P71:P122" si="35">IF(D71=0,"",O71*10^J71)</f>
+        <f t="shared" ref="P71:P122" si="36">IF(D71=0,"",O71*10^J71)</f>
         <v/>
       </c>
       <c r="Q71" s="57" t="str">
-        <f t="shared" ref="Q71:Q122" si="36">IF(D71=0,"",F71*N71*$J$7/$J$22)</f>
+        <f t="shared" ref="Q71:Q122" si="37">IF(D71=0,"",F71*N71*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R71" s="7"/>
@@ -17960,42 +17972,42 @@
       <c r="D72" s="48"/>
       <c r="E72" s="48"/>
       <c r="F72" s="58"/>
-      <c r="G72" s="143"/>
-      <c r="H72" s="143"/>
+      <c r="G72" s="173"/>
+      <c r="H72" s="173"/>
       <c r="I72" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J72" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K72" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L72" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M72" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N72" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O72" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P72" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q72" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R72" s="7"/>
@@ -18021,42 +18033,42 @@
       <c r="D73" s="48"/>
       <c r="E73" s="48"/>
       <c r="F73" s="58"/>
-      <c r="G73" s="143"/>
-      <c r="H73" s="143"/>
+      <c r="G73" s="173"/>
+      <c r="H73" s="173"/>
       <c r="I73" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J73" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K73" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L73" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M73" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N73" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O73" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P73" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q73" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R73" s="7"/>
@@ -18082,42 +18094,42 @@
       <c r="D74" s="48"/>
       <c r="E74" s="48"/>
       <c r="F74" s="58"/>
-      <c r="G74" s="143"/>
-      <c r="H74" s="143"/>
+      <c r="G74" s="173"/>
+      <c r="H74" s="173"/>
       <c r="I74" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J74" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K74" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L74" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M74" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N74" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O74" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P74" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q74" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R74" s="7"/>
@@ -18143,42 +18155,42 @@
       <c r="D75" s="48"/>
       <c r="E75" s="48"/>
       <c r="F75" s="58"/>
-      <c r="G75" s="143"/>
-      <c r="H75" s="143"/>
+      <c r="G75" s="173"/>
+      <c r="H75" s="173"/>
       <c r="I75" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J75" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K75" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L75" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M75" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N75" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O75" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P75" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q75" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R75" s="7"/>
@@ -18204,42 +18216,42 @@
       <c r="D76" s="48"/>
       <c r="E76" s="48"/>
       <c r="F76" s="58"/>
-      <c r="G76" s="143"/>
-      <c r="H76" s="143"/>
+      <c r="G76" s="173"/>
+      <c r="H76" s="173"/>
       <c r="I76" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J76" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K76" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L76" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M76" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N76" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O76" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P76" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q76" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R76" s="7"/>
@@ -18265,42 +18277,42 @@
       <c r="D77" s="48"/>
       <c r="E77" s="48"/>
       <c r="F77" s="58"/>
-      <c r="G77" s="143"/>
-      <c r="H77" s="143"/>
+      <c r="G77" s="173"/>
+      <c r="H77" s="173"/>
       <c r="I77" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J77" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K77" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L77" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M77" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N77" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O77" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P77" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q77" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R77" s="7"/>
@@ -18329,39 +18341,39 @@
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J78" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K78" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L78" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M78" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N78" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O78" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P78" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q78" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R78" s="7"/>
@@ -18390,39 +18402,39 @@
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J79" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K79" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L79" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M79" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N79" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O79" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P79" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q79" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R79" s="7"/>
@@ -18451,39 +18463,39 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J80" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K80" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L80" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M80" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N80" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O80" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P80" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q80" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R80" s="7"/>
@@ -18512,39 +18524,39 @@
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J81" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K81" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L81" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M81" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N81" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O81" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P81" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q81" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R81" s="7"/>
@@ -18573,39 +18585,39 @@
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J82" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K82" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L82" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M82" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N82" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O82" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P82" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q82" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R82" s="7"/>
@@ -18634,39 +18646,39 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J83" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K83" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L83" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M83" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N83" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O83" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P83" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q83" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R83" s="7"/>
@@ -18695,39 +18707,39 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J84" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K84" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L84" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M84" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N84" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O84" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P84" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q84" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R84" s="7"/>
@@ -18756,39 +18768,39 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J85" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K85" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L85" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M85" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N85" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O85" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P85" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q85" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R85" s="7"/>
@@ -18817,39 +18829,39 @@
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J86" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K86" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L86" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M86" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N86" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O86" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P86" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q86" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R86" s="7"/>
@@ -18878,39 +18890,39 @@
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J87" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K87" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L87" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M87" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N87" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O87" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P87" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q87" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R87" s="7"/>
@@ -18939,39 +18951,39 @@
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J88" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K88" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L88" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M88" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N88" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O88" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P88" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q88" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R88" s="7"/>
@@ -19000,39 +19012,39 @@
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J89" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K89" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L89" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M89" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N89" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O89" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P89" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q89" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R89" s="7"/>
@@ -19061,39 +19073,39 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J90" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K90" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L90" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M90" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N90" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O90" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P90" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q90" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R90" s="7"/>
@@ -19122,39 +19134,39 @@
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J91" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K91" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L91" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M91" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N91" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O91" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P91" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q91" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R91" s="7"/>
@@ -19183,39 +19195,39 @@
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J92" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K92" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L92" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M92" s="56" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N92" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O92" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P92" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q92" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R92" s="7"/>
@@ -19244,39 +19256,39 @@
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J93" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K93" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L93" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M93" s="56" t="str">
-        <f t="shared" ref="M93:M127" si="37">IF(D93=0,"",1-L93)</f>
+        <f t="shared" ref="M93:M127" si="38">IF(D93=0,"",1-L93)</f>
         <v/>
       </c>
       <c r="N93" s="56" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O93" s="57" t="str">
-        <f t="shared" ref="O93:O127" si="38">IF(D93=0,"",F93*K93*$J$7/$J$14)</f>
+        <f t="shared" ref="O93:O127" si="39">IF(D93=0,"",F93*K93*$J$7/$J$14)</f>
         <v/>
       </c>
       <c r="P93" s="57" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q93" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R93" s="7"/>
@@ -19305,39 +19317,39 @@
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J94" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K94" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L94" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M94" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N94" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O94" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P94" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q94" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N94" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O94" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P94" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q94" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R94" s="7"/>
@@ -19366,39 +19378,39 @@
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J95" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K95" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L95" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M95" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N95" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O95" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P95" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q95" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N95" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O95" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P95" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q95" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R95" s="7"/>
@@ -19427,39 +19439,39 @@
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J96" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K96" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L96" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M96" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N96" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O96" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P96" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q96" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N96" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O96" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P96" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q96" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R96" s="7"/>
@@ -19488,39 +19500,39 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J97" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K97" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L97" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M97" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N97" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O97" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P97" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q97" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N97" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O97" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P97" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q97" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R97" s="7"/>
@@ -19549,39 +19561,39 @@
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J98" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K98" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L98" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M98" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N98" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O98" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P98" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q98" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N98" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O98" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P98" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q98" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R98" s="7"/>
@@ -19610,39 +19622,39 @@
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J99" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K99" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L99" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M99" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N99" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O99" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P99" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q99" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N99" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O99" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P99" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q99" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R99" s="7"/>
@@ -19671,39 +19683,39 @@
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J100" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K100" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L100" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M100" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N100" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O100" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P100" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q100" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N100" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O100" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P100" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q100" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R100" s="7"/>
@@ -19732,39 +19744,39 @@
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J101" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K101" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L101" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M101" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N101" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O101" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P101" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q101" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N101" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O101" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P101" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q101" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R101" s="7"/>
@@ -19793,39 +19805,39 @@
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J102" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K102" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L102" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M102" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N102" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O102" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P102" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q102" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N102" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O102" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P102" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q102" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R102" s="7"/>
@@ -19854,39 +19866,39 @@
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J103" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K103" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L103" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M103" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N103" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O103" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P103" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q103" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N103" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O103" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P103" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q103" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R103" s="7"/>
@@ -19915,39 +19927,39 @@
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J104" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K104" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L104" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M104" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N104" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O104" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P104" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q104" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N104" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O104" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P104" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q104" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R104" s="7"/>
@@ -19976,39 +19988,39 @@
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J105" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K105" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L105" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M105" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N105" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O105" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P105" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q105" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N105" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O105" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P105" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q105" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R105" s="7"/>
@@ -20037,39 +20049,39 @@
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J106" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K106" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L106" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M106" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N106" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O106" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P106" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q106" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N106" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O106" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P106" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q106" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R106" s="7"/>
@@ -20098,39 +20110,39 @@
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J107" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K107" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L107" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M107" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N107" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O107" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P107" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q107" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N107" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O107" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P107" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q107" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R107" s="7"/>
@@ -20159,39 +20171,39 @@
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J108" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K108" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L108" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M108" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N108" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O108" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P108" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q108" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N108" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O108" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P108" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q108" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R108" s="7"/>
@@ -20220,39 +20232,39 @@
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J109" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K109" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L109" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M109" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N109" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O109" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P109" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q109" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N109" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O109" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P109" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q109" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R109" s="7"/>
@@ -20281,39 +20293,39 @@
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J110" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K110" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L110" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M110" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N110" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O110" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P110" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q110" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N110" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O110" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P110" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q110" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R110" s="7"/>
@@ -20342,39 +20354,39 @@
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J111" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K111" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L111" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M111" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N111" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O111" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P111" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q111" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N111" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O111" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P111" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q111" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R111" s="7"/>
@@ -20403,39 +20415,39 @@
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J112" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K112" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L112" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M112" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N112" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O112" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P112" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q112" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N112" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O112" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P112" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q112" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R112" s="7"/>
@@ -20464,39 +20476,39 @@
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
       <c r="I113" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J113" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K113" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L113" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M113" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N113" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O113" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P113" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q113" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N113" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O113" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P113" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q113" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R113" s="7"/>
@@ -20525,39 +20537,39 @@
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J114" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K114" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L114" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M114" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N114" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O114" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P114" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q114" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N114" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O114" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P114" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q114" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R114" s="7"/>
@@ -20586,39 +20598,39 @@
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J115" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K115" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L115" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M115" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N115" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O115" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P115" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q115" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N115" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O115" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P115" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q115" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R115" s="7"/>
@@ -20647,39 +20659,39 @@
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J116" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K116" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L116" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M116" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N116" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O116" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P116" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q116" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N116" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O116" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P116" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q116" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R116" s="7"/>
@@ -20708,39 +20720,39 @@
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
       <c r="I117" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J117" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K117" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L117" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M117" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N117" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O117" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P117" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q117" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N117" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O117" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P117" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q117" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R117" s="7"/>
@@ -20769,39 +20781,39 @@
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J118" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K118" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L118" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M118" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N118" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O118" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P118" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q118" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N118" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O118" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P118" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q118" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R118" s="7"/>
@@ -20830,39 +20842,39 @@
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
       <c r="I119" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J119" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K119" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L119" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M119" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N119" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O119" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P119" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q119" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N119" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O119" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P119" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q119" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R119" s="7"/>
@@ -20891,39 +20903,39 @@
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J120" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K120" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L120" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M120" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N120" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O120" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P120" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q120" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N120" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O120" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P120" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q120" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R120" s="7"/>
@@ -20952,39 +20964,39 @@
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J121" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K121" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L121" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M121" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N121" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O121" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P121" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q121" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N121" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O121" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P121" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q121" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R121" s="7"/>
@@ -21013,39 +21025,39 @@
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="55" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J122" s="55" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K122" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L122" s="56" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M122" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N122" s="56" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O122" s="57" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P122" s="57" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q122" s="57" t="str">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N122" s="56" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O122" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P122" s="57" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q122" s="57" t="str">
-        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="R122" s="7"/>
@@ -21074,39 +21086,39 @@
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
       <c r="I123" s="55" t="str">
-        <f t="shared" ref="I123:I127" si="39">IF(D123=0,"",LOG($K$15*10^D123+$K$16*10^E123+$K$14))</f>
+        <f t="shared" ref="I123:I127" si="40">IF(D123=0,"",LOG($K$15*10^D123+$K$16*10^E123+$K$14))</f>
         <v/>
       </c>
       <c r="J123" s="55" t="str">
-        <f t="shared" ref="J123:J127" si="40">IF(D123=0,"",LOG($K$21*10^D123+$K$22*10^E123+$K$20))</f>
+        <f t="shared" ref="J123:J127" si="41">IF(D123=0,"",LOG($K$21*10^D123+$K$22*10^E123+$K$20))</f>
         <v/>
       </c>
       <c r="K123" s="56" t="str">
-        <f t="shared" ref="K123:K127" si="41">IF(D123=0,"",1/(1+10^D123*$J$15/$J$14+10^E123*$J$16/$J$14+10^J123*$J$19/$J$14))</f>
+        <f t="shared" ref="K123:K127" si="42">IF(D123=0,"",1/(1+10^D123*$J$15/$J$14+10^E123*$J$16/$J$14+10^J123*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L123" s="56" t="str">
-        <f t="shared" ref="L123:L127" si="42">IF(D123=0,"",1/(1+10^I123/10^J123*$J$13/$J$19))</f>
+        <f t="shared" ref="L123:L127" si="43">IF(D123=0,"",1/(1+10^I123/10^J123*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M123" s="56" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N123" s="56" t="str">
-        <f t="shared" ref="N123:N127" si="43">IF(D123=0,"",1/(1/10^E123*$J$20/$J$22+10^D123/10^E123*$J$21/$J$22+10^I123/10^E123*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N123:N127" si="44">IF(D123=0,"",1/(1/10^E123*$J$20/$J$22+10^D123/10^E123*$J$21/$J$22+10^I123/10^E123*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O123" s="57" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P123" s="57" t="str">
-        <f t="shared" ref="P123:P127" si="44">IF(D123=0,"",O123*10^J123)</f>
+        <f t="shared" ref="P123:P127" si="45">IF(D123=0,"",O123*10^J123)</f>
         <v/>
       </c>
       <c r="Q123" s="57" t="str">
-        <f t="shared" ref="Q123:Q127" si="45">IF(D123=0,"",F123*N123*$J$7/$J$22)</f>
+        <f t="shared" ref="Q123:Q127" si="46">IF(D123=0,"",F123*N123*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R123" s="7"/>
@@ -21135,39 +21147,39 @@
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
       <c r="I124" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="J124" s="55" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="K124" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L124" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="M124" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N124" s="56" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="O124" s="57" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="J124" s="55" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K124" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="L124" s="56" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="M124" s="56" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N124" s="56" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="O124" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
       <c r="P124" s="57" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q124" s="57" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="R124" s="7"/>
@@ -21196,39 +21208,39 @@
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
       <c r="I125" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="J125" s="55" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="K125" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L125" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="M125" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N125" s="56" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="O125" s="57" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="J125" s="55" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K125" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="L125" s="56" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="M125" s="56" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N125" s="56" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="O125" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
       <c r="P125" s="57" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q125" s="57" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="R125" s="7"/>
@@ -21257,39 +21269,39 @@
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
       <c r="I126" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="J126" s="55" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="K126" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L126" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="M126" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N126" s="56" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="O126" s="57" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="J126" s="55" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K126" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="L126" s="56" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="M126" s="56" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N126" s="56" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="O126" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
       <c r="P126" s="57" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q126" s="57" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="R126" s="7"/>
@@ -21318,39 +21330,39 @@
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
       <c r="I127" s="55" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="J127" s="55" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="K127" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L127" s="56" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="M127" s="56" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="N127" s="56" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="O127" s="57" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="J127" s="55" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K127" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="L127" s="56" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="M127" s="56" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N127" s="56" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="O127" s="57" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
       <c r="P127" s="57" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q127" s="57" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="R127" s="7"/>
@@ -24979,6 +24991,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="L15:Q15"/>
+    <mergeCell ref="L16:Q16"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="G1:H77"/>
+    <mergeCell ref="L22:Q22"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="L6:Q6"/>
+    <mergeCell ref="L7:Q7"/>
+    <mergeCell ref="B24:F25"/>
+    <mergeCell ref="I17:Q17"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="I2:Q4"/>
     <mergeCell ref="I5:Q5"/>
     <mergeCell ref="B23:F23"/>
@@ -24995,42 +25043,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B8:F10"/>
     <mergeCell ref="B11:F12"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="L14:Q14"/>
-    <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="L16:Q16"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="G1:H77"/>
-    <mergeCell ref="L22:Q22"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="L6:Q6"/>
-    <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="B24:F25"/>
-    <mergeCell ref="I17:Q17"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
